--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D233262B-1DFC-4FD8-A69F-C3D492A58B74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389C36E1-6829-4348-BCE6-D2633B217DE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -952,6 +952,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="13">
+        <v>54</v>
+      </c>
+      <c r="F8" s="13">
+        <v>5</v>
+      </c>
+      <c r="G8" s="13">
+        <v>53</v>
+      </c>
+      <c r="H8" s="13">
+        <v>52</v>
+      </c>
+      <c r="I8" s="13">
+        <v>49</v>
+      </c>
+      <c r="J8" s="13">
+        <v>52</v>
+      </c>
+      <c r="K8" s="13">
+        <v>51</v>
+      </c>
+      <c r="L8" s="13">
+        <v>5</v>
+      </c>
+      <c r="M8" s="13">
+        <v>5</v>
+      </c>
+      <c r="N8" s="13">
+        <v>22</v>
+      </c>
+      <c r="O8" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="P8" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -967,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1282,6 +1332,47 @@
       </c>
       <c r="M7" s="9">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="K8" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="L8" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M8" s="9">
+        <v>1.1499999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1612,6 +1703,47 @@
         <v>0.41</v>
       </c>
       <c r="M7" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="M8" s="9">
         <v>0.42</v>
       </c>
     </row>
@@ -1629,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1892,6 +2024,38 @@
         <v>0.7</v>
       </c>
       <c r="J7" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="J8" s="9">
         <v>0.76</v>
       </c>
     </row>
@@ -1909,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2229,6 +2393,47 @@
         <v>9</v>
       </c>
       <c r="M7" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46085</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="13">
+        <v>12</v>
+      </c>
+      <c r="F8" s="13">
+        <v>11</v>
+      </c>
+      <c r="G8" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="13">
+        <v>19</v>
+      </c>
+      <c r="I8" s="13">
+        <v>18</v>
+      </c>
+      <c r="J8" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="K8" s="13">
+        <v>10</v>
+      </c>
+      <c r="L8" s="13">
+        <v>9</v>
+      </c>
+      <c r="M8" s="11">
         <v>9.5</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389C36E1-6829-4348-BCE6-D2633B217DE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F14F902-E691-4090-9ADB-58336377908A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -709,7 +709,7 @@
         <v>54</v>
       </c>
       <c r="F3" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G3" s="12">
         <v>53</v>
@@ -727,10 +727,10 @@
         <v>51</v>
       </c>
       <c r="L3" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M3" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N3" s="12">
         <v>22</v>
@@ -764,7 +764,7 @@
         <v>54</v>
       </c>
       <c r="F4" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G4" s="12">
         <v>53</v>
@@ -782,10 +782,10 @@
         <v>51</v>
       </c>
       <c r="L4" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M4" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N4" s="12">
         <v>22</v>
@@ -818,8 +818,8 @@
       <c r="E5" s="13">
         <v>54</v>
       </c>
-      <c r="F5" s="13">
-        <v>5</v>
+      <c r="F5" s="12">
+        <v>50</v>
       </c>
       <c r="G5" s="13">
         <v>53</v>
@@ -836,11 +836,11 @@
       <c r="K5" s="13">
         <v>51</v>
       </c>
-      <c r="L5" s="13">
-        <v>5</v>
-      </c>
-      <c r="M5" s="13">
-        <v>5</v>
+      <c r="L5" s="12">
+        <v>50</v>
+      </c>
+      <c r="M5" s="12">
+        <v>50</v>
       </c>
       <c r="N5" s="13">
         <v>22</v>
@@ -868,8 +868,8 @@
       <c r="E6" s="13">
         <v>54</v>
       </c>
-      <c r="F6" s="13">
-        <v>5</v>
+      <c r="F6" s="12">
+        <v>50</v>
       </c>
       <c r="G6" s="13">
         <v>53</v>
@@ -886,11 +886,11 @@
       <c r="K6" s="13">
         <v>51</v>
       </c>
-      <c r="L6" s="13">
-        <v>5</v>
-      </c>
-      <c r="M6" s="13">
-        <v>5</v>
+      <c r="L6" s="12">
+        <v>50</v>
+      </c>
+      <c r="M6" s="12">
+        <v>50</v>
       </c>
       <c r="N6" s="13">
         <v>22</v>
@@ -918,8 +918,8 @@
       <c r="E7" s="13">
         <v>54</v>
       </c>
-      <c r="F7" s="13">
-        <v>5</v>
+      <c r="F7" s="12">
+        <v>50</v>
       </c>
       <c r="G7" s="13">
         <v>53</v>
@@ -936,11 +936,11 @@
       <c r="K7" s="13">
         <v>51</v>
       </c>
-      <c r="L7" s="13">
-        <v>5</v>
-      </c>
-      <c r="M7" s="13">
-        <v>5</v>
+      <c r="L7" s="12">
+        <v>50</v>
+      </c>
+      <c r="M7" s="12">
+        <v>50</v>
       </c>
       <c r="N7" s="13">
         <v>22</v>
@@ -968,8 +968,8 @@
       <c r="E8" s="13">
         <v>54</v>
       </c>
-      <c r="F8" s="13">
-        <v>5</v>
+      <c r="F8" s="12">
+        <v>50</v>
       </c>
       <c r="G8" s="13">
         <v>53</v>
@@ -986,11 +986,11 @@
       <c r="K8" s="13">
         <v>51</v>
       </c>
-      <c r="L8" s="13">
-        <v>5</v>
-      </c>
-      <c r="M8" s="13">
-        <v>5</v>
+      <c r="L8" s="12">
+        <v>50</v>
+      </c>
+      <c r="M8" s="12">
+        <v>50</v>
       </c>
       <c r="N8" s="13">
         <v>22</v>
@@ -999,6 +999,56 @@
         <v>13.1</v>
       </c>
       <c r="P8" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="13">
+        <v>53</v>
+      </c>
+      <c r="F9" s="13">
+        <v>43</v>
+      </c>
+      <c r="G9" s="13">
+        <v>47</v>
+      </c>
+      <c r="H9" s="13">
+        <v>52</v>
+      </c>
+      <c r="I9" s="13">
+        <v>42</v>
+      </c>
+      <c r="J9" s="13">
+        <v>45</v>
+      </c>
+      <c r="K9" s="13">
+        <v>45</v>
+      </c>
+      <c r="L9" s="13">
+        <v>43</v>
+      </c>
+      <c r="M9" s="13">
+        <v>44</v>
+      </c>
+      <c r="N9" s="13">
+        <v>22</v>
+      </c>
+      <c r="O9" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="P9" s="11">
         <v>17.5</v>
       </c>
     </row>
@@ -1017,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1372,6 +1422,47 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="M8" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L9" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M9" s="9">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -1389,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1745,6 +1836,47 @@
       </c>
       <c r="M8" s="9">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2056,6 +2188,38 @@
         <v>0.7</v>
       </c>
       <c r="J8" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="J9" s="9">
         <v>0.76</v>
       </c>
     </row>
@@ -2073,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2434,6 +2598,47 @@
         <v>9</v>
       </c>
       <c r="M8" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="13">
+        <v>12</v>
+      </c>
+      <c r="F9" s="13">
+        <v>11</v>
+      </c>
+      <c r="G9" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="H9" s="13">
+        <v>19</v>
+      </c>
+      <c r="I9" s="13">
+        <v>18</v>
+      </c>
+      <c r="J9" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="K9" s="13">
+        <v>10</v>
+      </c>
+      <c r="L9" s="13">
+        <v>9</v>
+      </c>
+      <c r="M9" s="11">
         <v>9.5</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F14F902-E691-4090-9ADB-58336377908A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7DAE23-2EB9-4A74-A172-CF0DE54F2219}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1052,6 +1052,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="13">
+        <v>47</v>
+      </c>
+      <c r="F10" s="13">
+        <v>41</v>
+      </c>
+      <c r="G10" s="13">
+        <v>45</v>
+      </c>
+      <c r="H10" s="13">
+        <v>45</v>
+      </c>
+      <c r="I10" s="13">
+        <v>39</v>
+      </c>
+      <c r="J10" s="13">
+        <v>43</v>
+      </c>
+      <c r="K10" s="13">
+        <v>42</v>
+      </c>
+      <c r="L10" s="13">
+        <v>39</v>
+      </c>
+      <c r="M10" s="13">
+        <v>40</v>
+      </c>
+      <c r="N10" s="13">
+        <v>22</v>
+      </c>
+      <c r="O10" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="P10" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -1067,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1464,6 +1514,47 @@
       </c>
       <c r="M9" s="9">
         <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="F10" s="9">
+        <v>1</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="J10" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M10" s="9">
+        <v>1.1000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1877,6 +1968,47 @@
       </c>
       <c r="M9" s="9">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2220,6 +2352,38 @@
         <v>0.7</v>
       </c>
       <c r="J9" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="J10" s="9">
         <v>0.76</v>
       </c>
     </row>
@@ -2237,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2639,6 +2803,47 @@
         <v>9</v>
       </c>
       <c r="M9" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="13">
+        <v>12</v>
+      </c>
+      <c r="F10" s="13">
+        <v>11</v>
+      </c>
+      <c r="G10" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="H10" s="13">
+        <v>19</v>
+      </c>
+      <c r="I10" s="13">
+        <v>18</v>
+      </c>
+      <c r="J10" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="K10" s="13">
+        <v>10</v>
+      </c>
+      <c r="L10" s="13">
+        <v>9</v>
+      </c>
+      <c r="M10" s="11">
         <v>9.5</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7DAE23-2EB9-4A74-A172-CF0DE54F2219}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A56BBD-1CB2-4DD7-A44D-2CEE88391BFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1102,6 +1102,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="13">
+        <v>39</v>
+      </c>
+      <c r="F11" s="13">
+        <v>37</v>
+      </c>
+      <c r="G11" s="13">
+        <v>39</v>
+      </c>
+      <c r="H11" s="13">
+        <v>37</v>
+      </c>
+      <c r="I11" s="13">
+        <v>35</v>
+      </c>
+      <c r="J11" s="13">
+        <v>37</v>
+      </c>
+      <c r="K11" s="13">
+        <v>37</v>
+      </c>
+      <c r="L11" s="13">
+        <v>35</v>
+      </c>
+      <c r="M11" s="13">
+        <v>37</v>
+      </c>
+      <c r="N11" s="13">
+        <v>22</v>
+      </c>
+      <c r="O11" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="P11" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -1117,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -1554,6 +1604,47 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="M10" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="J11" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="K11" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L11" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M11" s="9">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -1571,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2009,6 +2100,47 @@
       </c>
       <c r="M10" s="9">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.38</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.38</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0.38</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -2025,7 +2157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2384,6 +2516,38 @@
         <v>0.7</v>
       </c>
       <c r="J10" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="J11" s="9">
         <v>0.76</v>
       </c>
     </row>
@@ -2401,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
@@ -2844,6 +3008,47 @@
         <v>9</v>
       </c>
       <c r="M10" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46106</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="13">
+        <v>12</v>
+      </c>
+      <c r="F11" s="13">
+        <v>11</v>
+      </c>
+      <c r="G11" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="H11" s="13">
+        <v>19</v>
+      </c>
+      <c r="I11" s="13">
+        <v>18</v>
+      </c>
+      <c r="J11" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="K11" s="13">
+        <v>10</v>
+      </c>
+      <c r="L11" s="13">
+        <v>9</v>
+      </c>
+      <c r="M11" s="11">
         <v>9.5</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A56BBD-1CB2-4DD7-A44D-2CEE88391BFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7F1F0-86FE-47A4-95B2-174599E7AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -193,24 +193,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -223,7 +224,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -260,11 +261,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -273,38 +274,41 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -583,107 +587,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9" style="13"/>
-    <col min="15" max="16" width="9" style="11"/>
-    <col min="17" max="21" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9" style="12"/>
+    <col min="15" max="16" width="9" style="10"/>
+    <col min="17" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="12" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="Q2" s="4"/>
@@ -692,53 +696,53 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:21">
+      <c r="A3" s="16">
         <v>46043</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="16">
         <v>46043</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>54</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>50</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>53</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>52</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>49</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>52</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <v>51</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <v>50</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <v>50</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <v>22</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>13.1</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="9">
         <v>17.5</v>
       </c>
       <c r="Q3" s="4"/>
@@ -747,53 +751,53 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:21">
+      <c r="A4" s="16">
         <v>46050</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="16">
         <v>46050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>54</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>50</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>53</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>52</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>49</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>52</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>51</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>50</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>50</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>22</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>13.1</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>17.5</v>
       </c>
       <c r="Q4" s="4"/>
@@ -802,353 +806,353 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:21">
+      <c r="A5" s="16">
         <v>46057</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>46057</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>54</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>50</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>53</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>52</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>49</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>52</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>51</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <v>50</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="11">
         <v>50</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <v>22</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>13.1</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:21">
+      <c r="A6" s="16">
         <v>46064</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>46064</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="C6" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="12">
         <v>54</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>50</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>53</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>52</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>49</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>52</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>51</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <v>50</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="11">
         <v>50</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="12">
         <v>22</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <v>13.1</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:21">
+      <c r="A7" s="16">
         <v>46078</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>46078</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="C7" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12">
         <v>54</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>50</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>53</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>52</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <v>49</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <v>52</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="12">
         <v>51</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>50</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="11">
         <v>50</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="12">
         <v>22</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <v>13.1</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:21">
+      <c r="A8" s="16">
         <v>46085</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>46085</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="C8" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="12">
         <v>54</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>50</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>53</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>52</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <v>49</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <v>52</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <v>51</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="11">
         <v>50</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="11">
         <v>50</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="12">
         <v>22</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <v>13.1</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:21">
+      <c r="A9" s="16">
         <v>46092</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="16">
         <v>46092</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="C9" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
         <v>53</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>43</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>47</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>52</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>42</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>45</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>45</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>43</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <v>44</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="12">
         <v>22</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <v>13.1</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:21">
+      <c r="A10" s="16">
         <v>46099</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>46099</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="C10" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
         <v>47</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>41</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>45</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>45</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <v>39</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <v>43</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="12">
         <v>42</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="12">
         <v>39</v>
       </c>
-      <c r="M10" s="13">
-        <v>40</v>
-      </c>
-      <c r="N10" s="13">
+      <c r="M10" s="12">
+        <v>40</v>
+      </c>
+      <c r="N10" s="12">
         <v>22</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="10">
         <v>13.1</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="10">
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:21">
+      <c r="A11" s="16">
         <v>46106</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>46106</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="C11" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
         <v>39</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>37</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>39</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>37</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>35</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <v>37</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <v>37</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="12">
         <v>35</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <v>37</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="12">
         <v>22</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="10">
         <v>13.1</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -1168,27 +1172,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1222,11 +1226,11 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -1263,17 +1267,17 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:21">
+      <c r="A3" s="16">
         <v>46043</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="16">
         <v>46043</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="4">
@@ -1312,17 +1316,17 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:21">
+      <c r="A4" s="16">
         <v>46050</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="16">
         <v>46050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="4">
@@ -1361,290 +1365,290 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:21">
+      <c r="A5" s="16">
         <v>46057</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>46057</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="8">
         <v>1.25</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>1.2</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>1.55</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>1.4</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>1.5</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>1.35</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>1.2</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:21">
+      <c r="A6" s="16">
         <v>46064</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>46064</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8">
         <v>1.25</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>1.2</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>1.55</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>1.4</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>1.5</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="8">
         <v>1.35</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <v>1.2</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="8">
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:21">
+      <c r="A7" s="16">
         <v>46078</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>46078</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="8">
         <v>1.25</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>1.2</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>1.55</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>1.4</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>1.5</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="8">
         <v>1.35</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <v>1.2</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:21">
+      <c r="A8" s="16">
         <v>46085</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>46085</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>1.05</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>1.05</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>1.4</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>1.35</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>1.35</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <v>1.2</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:21">
+      <c r="A9" s="16">
         <v>46092</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="16">
         <v>46092</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>1.05</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>1.05</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>1.35</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>1.33</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>1.35</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:21">
+      <c r="A10" s="16">
         <v>46099</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>46099</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="8">
         <v>1.05</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>1</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>1</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>1.35</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>1.3</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>1.3</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:21">
+      <c r="A11" s="16">
         <v>46106</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>46106</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="8">
         <v>1</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>0.98</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>1</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>1.3</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>1.25</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>1.25</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -1663,27 +1667,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1717,11 +1721,11 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -1758,17 +1762,17 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:21">
+      <c r="A3" s="16">
         <v>46043</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="16">
         <v>46043</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="4">
@@ -1807,17 +1811,17 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:21">
+      <c r="A4" s="16">
         <v>46050</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="16">
         <v>46050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="4">
@@ -1856,76 +1860,76 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:21">
+      <c r="A5" s="16">
         <v>46057</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>46057</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="8">
         <v>0.43</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>0.41</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>0.42</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0.43</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.41</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.42</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>0.43</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>0.41</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:21">
+      <c r="A6" s="16">
         <v>46064</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>46064</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8">
         <v>0.43</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>0.41</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>0.42</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>0.43</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>0.41</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0.42</v>
       </c>
       <c r="K6" s="4">
@@ -1938,208 +1942,208 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:21">
+      <c r="A7" s="16">
         <v>46078</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>46078</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="8">
         <v>0.43</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>0.41</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>0.42</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>0.43</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>0.41</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0.42</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="8">
         <v>0.43</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <v>0.41</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:21">
+      <c r="A8" s="16">
         <v>46085</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>46085</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="8">
         <v>0.43</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>0.41</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>0.42</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>0.43</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>0.41</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0.42</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <v>0.43</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>0.41</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:21">
+      <c r="A9" s="16">
         <v>46092</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="16">
         <v>46092</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="8">
         <v>0.42</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>0.4</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>0.41</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>0.42</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>0.4</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0.41</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="8">
         <v>0.42</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <v>0.4</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:21">
+      <c r="A10" s="16">
         <v>46099</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>46099</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="8">
         <v>0.41</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>0.39</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>0.4</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>0.41</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>0.39</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0.4</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="8">
         <v>0.41</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="8">
         <v>0.39500000000000002</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:21">
+      <c r="A11" s="16">
         <v>46106</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>46106</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="8">
         <v>0.39500000000000002</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>0.38</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>0.39</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>0.39</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>0.38</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0.39</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="8">
         <v>0.39500000000000002</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <v>0.38</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <v>0.39</v>
       </c>
     </row>
@@ -2158,27 +2162,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -2206,11 +2210,11 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -2241,17 +2245,17 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:21">
+      <c r="A3" s="16">
         <v>46043</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="16">
         <v>46043</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="4">
@@ -2284,17 +2288,17 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:21">
+      <c r="A4" s="16">
         <v>46050</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="16">
         <v>46050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="4">
@@ -2327,227 +2331,227 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:21">
+      <c r="A5" s="16">
         <v>46057</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>46057</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="8">
         <v>0.85</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>0.78</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>0.79</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0.82</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.7</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:21">
+      <c r="A6" s="16">
         <v>46064</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>46064</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8">
         <v>0.85</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>0.78</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>0.79</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>0.82</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>0.7</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:21">
+      <c r="A7" s="16">
         <v>46078</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>46078</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="8">
         <v>0.85</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>0.78</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>0.79</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>0.82</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>0.7</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:21">
+      <c r="A8" s="16">
         <v>46085</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>46085</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="8">
         <v>0.85</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>0.78</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>0.79</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>0.82</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>0.7</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:21">
+      <c r="A9" s="16">
         <v>46092</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="16">
         <v>46092</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="8">
         <v>0.85</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>0.78</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>0.79</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>0.82</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>0.7</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:21">
+      <c r="A10" s="16">
         <v>46099</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>46099</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="8">
         <v>0.85</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>0.78</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>0.79</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>0.82</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>0.7</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:21">
+      <c r="A11" s="16">
         <v>46106</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>46106</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="8">
         <v>0.85</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>0.78</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>0.79</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>0.82</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>0.7</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -2566,96 +2570,96 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="13"/>
-    <col min="7" max="7" width="9" style="11"/>
-    <col min="8" max="9" width="9" style="13"/>
-    <col min="10" max="10" width="9" style="11"/>
-    <col min="11" max="12" width="9" style="13"/>
-    <col min="13" max="13" width="9" style="11"/>
-    <col min="14" max="21" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="12"/>
+    <col min="7" max="7" width="9" style="10"/>
+    <col min="8" max="9" width="9" style="12"/>
+    <col min="10" max="10" width="9" style="10"/>
+    <col min="11" max="12" width="9" style="12"/>
+    <col min="13" max="13" width="9" style="10"/>
+    <col min="14" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>39</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="12" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="N2" s="4"/>
@@ -2667,44 +2671,44 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:21">
+      <c r="A3" s="16">
         <v>46043</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="16">
         <v>46043</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>12</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>11</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>11.5</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>19</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>18</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>18.5</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <v>10</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <v>9</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>9.5</v>
       </c>
       <c r="N3" s="4"/>
@@ -2716,44 +2720,44 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:21">
+      <c r="A4" s="16">
         <v>46050</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="16">
         <v>46050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>12</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>11</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>11.5</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>19</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>18</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>18.5</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>10</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>9</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>9.5</v>
       </c>
       <c r="N4" s="4"/>
@@ -2765,290 +2769,290 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:21">
+      <c r="A5" s="16">
         <v>46057</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>46057</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="13">
+      <c r="C5" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="12">
         <v>12</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>11</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>11.5</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>19</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>18</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>18.5</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>10</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>9</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:21">
+      <c r="A6" s="16">
         <v>46064</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>46064</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="C6" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="12">
         <v>12</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>11</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>11.5</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>19</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>18</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <v>18.5</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>10</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <v>9</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:21">
+      <c r="A7" s="16">
         <v>46078</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>46078</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="C7" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12">
         <v>12</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>11</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>11.5</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>19</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <v>18</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <v>18.5</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="12">
         <v>10</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <v>9</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:21">
+      <c r="A8" s="16">
         <v>46085</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>46085</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="C8" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="12">
         <v>12</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>11</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>11.5</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>19</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <v>18</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <v>18.5</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <v>10</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <v>9</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:21">
+      <c r="A9" s="16">
         <v>46092</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="16">
         <v>46092</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="C9" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
         <v>12</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>11</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>11.5</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>19</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>18</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>18.5</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>10</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>9</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:21">
+      <c r="A10" s="16">
         <v>46099</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>46099</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="C10" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
         <v>12</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>11</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>11.5</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>19</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <v>18</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <v>18.5</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="12">
         <v>10</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="12">
         <v>9</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="10">
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:21">
+      <c r="A11" s="16">
         <v>46106</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>46106</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.75694444444444497</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="C11" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
         <v>12</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>11</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>11.5</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>19</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>18</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <v>18.5</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <v>10</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="12">
         <v>9</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <v>9.5</v>
       </c>
     </row>
@@ -3067,18 +3071,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3086,25 +3090,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -3112,19 +3116,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -3132,19 +3136,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -3152,13 +3156,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -3166,13 +3170,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C511213D-20F8-4131-98FF-9CEF988A00D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CAD09A-E112-49E2-BE2A-18D37F91815C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -195,24 +198,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -225,7 +228,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -262,7 +265,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -275,32 +278,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -308,8 +311,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +330,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -416,7 +419,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$12</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -530,7 +533,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$12</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -644,7 +647,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$12</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -854,7 +857,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="961379087"/>
@@ -886,7 +889,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -914,7 +917,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="961366127"/>
@@ -956,13 +959,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -970,6 +972,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -991,7 +994,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ko-KR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1005,7 +1008,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1418,7 +1421,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183428623"/>
@@ -1479,7 +1482,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183437743"/>
@@ -1521,13 +1524,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1535,6 +1537,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1556,7 +1559,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ko-KR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1570,7 +1573,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1983,7 +1986,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183551503"/>
@@ -2043,7 +2046,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183551023"/>
@@ -2086,13 +2089,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2100,6 +2102,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2121,7 +2124,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ko-KR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2135,7 +2138,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2434,7 +2437,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183484783"/>
@@ -2494,7 +2497,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183493423"/>
@@ -2536,13 +2539,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2550,6 +2552,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2571,7 +2574,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ko-KR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2585,7 +2588,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2998,7 +3001,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183500623"/>
@@ -3059,7 +3062,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1183466543"/>
@@ -3101,13 +3104,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3115,6 +3117,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3136,7 +3139,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ko-KR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -6386,19 +6389,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -6448,7 +6451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -6495,7 +6498,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -6550,7 +6553,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -6605,7 +6608,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -6655,7 +6658,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -6705,7 +6708,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -6755,7 +6758,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -6805,7 +6808,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -6855,7 +6858,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -6905,7 +6908,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -6955,7 +6958,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7021,17 +7024,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7075,7 +7078,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7116,7 +7119,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7165,7 +7168,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7214,7 +7217,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7255,7 +7258,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7296,7 +7299,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7337,7 +7340,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7378,7 +7381,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7419,7 +7422,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7460,7 +7463,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -7501,7 +7504,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7557,17 +7560,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7611,7 +7614,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7652,7 +7655,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7701,7 +7704,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7750,7 +7753,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7791,7 +7794,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7832,7 +7835,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7873,7 +7876,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7914,7 +7917,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7955,7 +7958,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7996,7 +7999,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8037,7 +8040,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8093,17 +8096,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8141,7 +8144,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8176,7 +8179,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8219,7 +8222,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8262,7 +8265,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8294,7 +8297,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8326,7 +8329,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8358,7 +8361,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8390,7 +8393,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8454,7 +8457,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8486,7 +8489,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8533,12 +8536,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
     <col min="7" max="7" width="9" style="10"/>
     <col min="8" max="9" width="9" style="12"/>
@@ -8549,7 +8552,7 @@
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8593,7 +8596,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8634,7 +8637,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8683,7 +8686,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8732,7 +8735,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8773,7 +8776,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8814,7 +8817,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8855,7 +8858,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8896,7 +8899,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8937,7 +8940,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8978,7 +8981,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -9019,7 +9022,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -9075,28 +9078,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9104,25 +9109,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -9130,19 +9135,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -9150,19 +9155,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -9170,13 +9175,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -9184,13 +9189,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86974DEC-33C8-4FDB-9E42-46EFB1AFCC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDE9178-3DA1-4F7F-AA84-2189E2CC630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -415,6 +415,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -458,6 +461,9 @@
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -541,6 +547,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -584,6 +593,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -667,6 +679,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -710,6 +725,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -793,6 +811,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -836,6 +857,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1141,6 +1165,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1184,6 +1211,9 @@
                   <c:v>0.93</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1267,6 +1297,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1310,6 +1343,9 @@
                   <c:v>1.23</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1393,6 +1429,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1436,6 +1475,9 @@
                   <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1742,6 +1784,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1862,6 +1907,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1982,6 +2030,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2026,6 +2077,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.33500000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2332,6 +2386,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2375,6 +2432,9 @@
                   <c:v>0.79</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -2458,6 +2518,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2501,6 +2564,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2806,6 +2872,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2849,6 +2918,9 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2932,6 +3004,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2975,6 +3050,9 @@
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3058,6 +3136,9 @@
                 <c:pt idx="11">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3101,6 +3182,9 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6554,7 +6638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -7271,6 +7355,56 @@
         <v>13.1</v>
       </c>
       <c r="P14" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="12">
+        <v>39</v>
+      </c>
+      <c r="F15" s="12">
+        <v>35</v>
+      </c>
+      <c r="G15" s="12">
+        <v>37</v>
+      </c>
+      <c r="H15" s="12">
+        <v>37</v>
+      </c>
+      <c r="I15" s="12">
+        <v>33</v>
+      </c>
+      <c r="J15" s="12">
+        <v>35</v>
+      </c>
+      <c r="K15" s="12">
+        <v>36</v>
+      </c>
+      <c r="L15" s="12">
+        <v>32</v>
+      </c>
+      <c r="M15" s="12">
+        <v>34</v>
+      </c>
+      <c r="N15" s="12">
+        <v>22</v>
+      </c>
+      <c r="O15" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P15" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7289,7 +7423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -7890,6 +8024,47 @@
         <v>1</v>
       </c>
       <c r="M14" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L15" s="8">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -7907,7 +8082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -8509,6 +8684,47 @@
       </c>
       <c r="M14" s="8">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0.33500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -8525,7 +8741,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -9015,6 +9231,38 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9029,19 +9277,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="9" style="10"/>
-    <col min="8" max="9" width="9" style="12"/>
-    <col min="10" max="10" width="9" style="10"/>
-    <col min="11" max="12" width="9" style="12"/>
-    <col min="13" max="13" width="9" style="10"/>
+    <col min="5" max="5" width="9" style="10" customWidth="1"/>
+    <col min="6" max="13" width="9" style="10"/>
     <col min="14" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -9059,28 +9303,28 @@
       <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>38</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M1" s="9" t="s">
@@ -9095,28 +9339,28 @@
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
       <c r="D2" s="16"/>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="M2" s="9" t="s">
@@ -9144,28 +9388,28 @@
       <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>12</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <v>11</v>
       </c>
       <c r="G3" s="9">
         <v>11.5</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9">
         <v>19</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <v>18</v>
       </c>
       <c r="J3" s="9">
         <v>18.5</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="9">
         <v>10</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="9">
         <v>9</v>
       </c>
       <c r="M3" s="9">
@@ -9193,28 +9437,28 @@
       <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>12</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>11</v>
       </c>
       <c r="G4" s="9">
         <v>11.5</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="9">
         <v>19</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <v>18</v>
       </c>
       <c r="J4" s="9">
         <v>18.5</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="9">
         <v>10</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="9">
         <v>9</v>
       </c>
       <c r="M4" s="9">
@@ -9242,28 +9486,28 @@
       <c r="D5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>12</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>11</v>
       </c>
       <c r="G5" s="10">
         <v>11.5</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="10">
         <v>19</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="10">
         <v>18</v>
       </c>
       <c r="J5" s="10">
         <v>18.5</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="10">
         <v>10</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="10">
         <v>9</v>
       </c>
       <c r="M5" s="10">
@@ -9283,28 +9527,28 @@
       <c r="D6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>12</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>11</v>
       </c>
       <c r="G6" s="10">
         <v>11.5</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>19</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <v>18</v>
       </c>
       <c r="J6" s="10">
         <v>18.5</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="10">
         <v>10</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="10">
         <v>9</v>
       </c>
       <c r="M6" s="10">
@@ -9324,28 +9568,28 @@
       <c r="D7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>12</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>11</v>
       </c>
       <c r="G7" s="10">
         <v>11.5</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="10">
         <v>19</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="10">
         <v>18</v>
       </c>
       <c r="J7" s="10">
         <v>18.5</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="10">
         <v>10</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="10">
         <v>9</v>
       </c>
       <c r="M7" s="10">
@@ -9365,28 +9609,28 @@
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>12</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>11</v>
       </c>
       <c r="G8" s="10">
         <v>11.5</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="10">
         <v>19</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="10">
         <v>18</v>
       </c>
       <c r="J8" s="10">
         <v>18.5</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="10">
         <v>10</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="10">
         <v>9</v>
       </c>
       <c r="M8" s="10">
@@ -9406,28 +9650,28 @@
       <c r="D9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>12</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="10">
         <v>11</v>
       </c>
       <c r="G9" s="10">
         <v>11.5</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="10">
         <v>19</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="10">
         <v>18</v>
       </c>
       <c r="J9" s="10">
         <v>18.5</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="10">
         <v>10</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="10">
         <v>9</v>
       </c>
       <c r="M9" s="10">
@@ -9447,28 +9691,28 @@
       <c r="D10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>12</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>11</v>
       </c>
       <c r="G10" s="10">
         <v>11.5</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="10">
         <v>19</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="10">
         <v>18</v>
       </c>
       <c r="J10" s="10">
         <v>18.5</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="10">
         <v>10</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="10">
         <v>9</v>
       </c>
       <c r="M10" s="10">
@@ -9488,28 +9732,28 @@
       <c r="D11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="10">
         <v>12</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="10">
         <v>11</v>
       </c>
       <c r="G11" s="10">
         <v>11.5</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="10">
         <v>19</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="10">
         <v>18</v>
       </c>
       <c r="J11" s="10">
         <v>18.5</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="10">
         <v>10</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="10">
         <v>9</v>
       </c>
       <c r="M11" s="10">
@@ -9529,28 +9773,28 @@
       <c r="D12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>12</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="10">
         <v>11</v>
       </c>
       <c r="G12" s="10">
         <v>11.5</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="10">
         <v>19</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="10">
         <v>18</v>
       </c>
       <c r="J12" s="10">
         <v>18.5</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="10">
         <v>10</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="10">
         <v>9</v>
       </c>
       <c r="M12" s="10">
@@ -9570,28 +9814,28 @@
       <c r="D13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="10">
         <v>11.5</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="10">
         <v>10.5</v>
       </c>
       <c r="G13" s="10">
         <v>11</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="10">
         <v>18.5</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="10">
         <v>17.5</v>
       </c>
       <c r="J13" s="10">
         <v>18</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="10">
         <v>9.5</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="10">
         <v>8.5</v>
       </c>
       <c r="M13" s="10">
@@ -9611,31 +9855,72 @@
       <c r="D14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>11</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>10</v>
       </c>
       <c r="G14" s="10">
         <v>10.5</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="10">
         <v>18.5</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="10">
         <v>17</v>
       </c>
       <c r="J14" s="10">
         <v>17.75</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="10">
         <v>9</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="10">
         <v>8.5</v>
       </c>
       <c r="M14" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="10">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
+        <v>10</v>
+      </c>
+      <c r="G15" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H15" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I15" s="10">
+        <v>17</v>
+      </c>
+      <c r="J15" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K15" s="10">
+        <v>9</v>
+      </c>
+      <c r="L15" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M15" s="10">
         <v>8.75</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FABBDA9-CAEA-46E4-85DF-E4F13DF600D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB922E41-9C15-4545-94F3-847C3819DA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -421,6 +421,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -470,6 +473,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -559,6 +565,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -608,6 +617,9 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -697,6 +709,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -746,6 +761,9 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -835,6 +853,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -884,6 +905,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1195,6 +1219,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1244,6 +1271,9 @@
                   <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1333,6 +1363,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1382,6 +1415,9 @@
                   <c:v>1.23</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1471,6 +1507,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1520,6 +1559,9 @@
                   <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1832,6 +1874,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1958,6 +2003,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2084,6 +2132,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2133,6 +2184,9 @@
                   <c:v>0.33500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
@@ -2446,6 +2500,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2495,6 +2552,9 @@
                   <c:v>0.79</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.78</c:v>
                 </c:pt>
               </c:numCache>
@@ -2584,6 +2644,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2633,6 +2696,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2944,6 +3010,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2993,6 +3062,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3082,6 +3154,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3131,6 +3206,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3220,6 +3298,9 @@
                 <c:pt idx="13">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3269,6 +3350,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6722,7 +6806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -7539,6 +7623,56 @@
         <v>13.1</v>
       </c>
       <c r="P16" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="12">
+        <v>39</v>
+      </c>
+      <c r="F17" s="12">
+        <v>35</v>
+      </c>
+      <c r="G17" s="12">
+        <v>37</v>
+      </c>
+      <c r="H17" s="12">
+        <v>37</v>
+      </c>
+      <c r="I17" s="12">
+        <v>33</v>
+      </c>
+      <c r="J17" s="12">
+        <v>35</v>
+      </c>
+      <c r="K17" s="12">
+        <v>36</v>
+      </c>
+      <c r="L17" s="12">
+        <v>32</v>
+      </c>
+      <c r="M17" s="12">
+        <v>34</v>
+      </c>
+      <c r="N17" s="12">
+        <v>22</v>
+      </c>
+      <c r="O17" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P17" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7557,7 +7691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -8240,6 +8374,47 @@
         <v>1</v>
       </c>
       <c r="M16" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -8257,7 +8432,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -8940,6 +9115,47 @@
         <v>0.33</v>
       </c>
       <c r="M16" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M17" s="8">
         <v>0.33</v>
       </c>
     </row>
@@ -8957,7 +9173,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -9511,6 +9727,38 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9525,7 +9773,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -10210,6 +10458,47 @@
         <v>8.5</v>
       </c>
       <c r="M16" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="10">
+        <v>11</v>
+      </c>
+      <c r="F17" s="10">
+        <v>10</v>
+      </c>
+      <c r="G17" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H17" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I17" s="10">
+        <v>17</v>
+      </c>
+      <c r="J17" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K17" s="10">
+        <v>9</v>
+      </c>
+      <c r="L17" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M17" s="10">
         <v>8.75</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB922E41-9C15-4545-94F3-847C3819DA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F228B54-22D2-442D-966B-E03A22678980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -195,24 +195,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -225,7 +225,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -262,7 +262,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -275,32 +275,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -308,8 +308,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +327,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -424,6 +424,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -431,7 +434,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -476,6 +479,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -568,6 +574,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -575,7 +584,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -620,6 +629,9 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -712,6 +724,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -719,7 +734,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -764,6 +779,9 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -856,6 +874,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -908,6 +929,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1006,7 +1030,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1125,7 +1149,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1222,6 +1246,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1274,6 +1301,9 @@
                   <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1366,6 +1396,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1418,6 +1451,9 @@
                   <c:v>1.23</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1510,6 +1546,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1562,6 +1601,9 @@
                   <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1780,7 +1822,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1877,6 +1919,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2006,6 +2051,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2135,6 +2183,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2187,6 +2238,9 @@
                   <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
@@ -2406,7 +2460,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2503,6 +2557,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2555,6 +2612,9 @@
                   <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.78</c:v>
                 </c:pt>
               </c:numCache>
@@ -2647,6 +2707,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2699,6 +2762,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2916,7 +2982,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3013,6 +3079,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3065,6 +3134,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3157,6 +3229,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3209,6 +3284,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3301,6 +3379,9 @@
                 <c:pt idx="14">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3353,6 +3434,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6806,20 +6890,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -6869,7 +6953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -6916,7 +7000,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -6971,7 +7055,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7026,7 +7110,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7076,7 +7160,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7126,7 +7210,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7176,7 +7260,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7226,7 +7310,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7276,7 +7360,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7326,7 +7410,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -7376,7 +7460,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7426,7 +7510,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -7476,7 +7560,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21">
       <c r="A14" s="13">
         <v>46127</v>
       </c>
@@ -7526,7 +7610,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="13">
         <v>46134</v>
       </c>
@@ -7576,7 +7660,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="13">
         <v>46141</v>
       </c>
@@ -7626,7 +7710,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="13">
         <v>46155</v>
       </c>
@@ -7673,6 +7757,56 @@
         <v>13.1</v>
       </c>
       <c r="P17" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="12">
+        <v>39</v>
+      </c>
+      <c r="F18" s="12">
+        <v>35</v>
+      </c>
+      <c r="G18" s="12">
+        <v>37</v>
+      </c>
+      <c r="H18" s="12">
+        <v>37</v>
+      </c>
+      <c r="I18" s="12">
+        <v>33</v>
+      </c>
+      <c r="J18" s="12">
+        <v>35</v>
+      </c>
+      <c r="K18" s="12">
+        <v>36</v>
+      </c>
+      <c r="L18" s="12">
+        <v>32</v>
+      </c>
+      <c r="M18" s="12">
+        <v>34</v>
+      </c>
+      <c r="N18" s="12">
+        <v>22</v>
+      </c>
+      <c r="O18" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P18" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7691,18 +7825,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7746,7 +7880,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7787,7 +7921,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7836,7 +7970,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7885,7 +8019,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7926,7 +8060,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7967,7 +8101,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8008,7 +8142,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8049,7 +8183,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8090,7 +8224,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8131,7 +8265,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8172,7 +8306,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8213,7 +8347,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -8254,7 +8388,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21">
       <c r="A14" s="13">
         <v>46127</v>
       </c>
@@ -8295,7 +8429,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="13">
         <v>46134</v>
       </c>
@@ -8336,7 +8470,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="13">
         <v>46141</v>
       </c>
@@ -8377,7 +8511,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="13">
         <v>46155</v>
       </c>
@@ -8415,6 +8549,47 @@
         <v>1</v>
       </c>
       <c r="M17" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H18" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L18" s="8">
+        <v>1</v>
+      </c>
+      <c r="M18" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -8432,18 +8607,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8487,7 +8662,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8528,7 +8703,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8577,7 +8752,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8626,7 +8801,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8667,7 +8842,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8708,7 +8883,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8749,7 +8924,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8790,7 +8965,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8831,7 +9006,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8872,7 +9047,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8913,7 +9088,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8954,7 +9129,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -8995,7 +9170,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21">
       <c r="A14" s="13">
         <v>46127</v>
       </c>
@@ -9036,7 +9211,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="13">
         <v>46134</v>
       </c>
@@ -9077,7 +9252,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="13">
         <v>46141</v>
       </c>
@@ -9118,7 +9293,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="13">
         <v>46155</v>
       </c>
@@ -9156,6 +9331,47 @@
         <v>0.33</v>
       </c>
       <c r="M17" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M18" s="8">
         <v>0.33</v>
       </c>
     </row>
@@ -9173,18 +9389,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -9222,7 +9438,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -9257,7 +9473,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -9300,7 +9516,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -9343,7 +9559,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -9375,7 +9591,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -9407,7 +9623,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -9439,7 +9655,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -9471,7 +9687,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -9503,7 +9719,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -9535,7 +9751,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -9567,7 +9783,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -9599,7 +9815,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -9631,7 +9847,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21">
       <c r="A14" s="13">
         <v>46127</v>
       </c>
@@ -9663,7 +9879,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="13">
         <v>46134</v>
       </c>
@@ -9695,7 +9911,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="13">
         <v>46141</v>
       </c>
@@ -9727,7 +9943,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="13">
         <v>46155</v>
       </c>
@@ -9756,6 +9972,38 @@
         <v>0.75</v>
       </c>
       <c r="J17" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J18" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -9773,20 +10021,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="10" customWidth="1"/>
     <col min="6" max="13" width="9" style="10"/>
     <col min="14" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -9830,7 +10078,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -9871,7 +10119,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -9920,7 +10168,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -9969,7 +10217,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -10010,7 +10258,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -10051,7 +10299,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -10092,7 +10340,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -10133,7 +10381,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -10174,7 +10422,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -10215,7 +10463,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -10256,7 +10504,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -10297,7 +10545,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -10338,7 +10586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21">
       <c r="A14" s="13">
         <v>46127</v>
       </c>
@@ -10379,7 +10627,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="13">
         <v>46134</v>
       </c>
@@ -10420,7 +10668,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="13">
         <v>46141</v>
       </c>
@@ -10461,7 +10709,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="13">
         <v>46155</v>
       </c>
@@ -10499,6 +10747,47 @@
         <v>8.5</v>
       </c>
       <c r="M17" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="10">
+        <v>11</v>
+      </c>
+      <c r="F18" s="10">
+        <v>10</v>
+      </c>
+      <c r="G18" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H18" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I18" s="10">
+        <v>17</v>
+      </c>
+      <c r="J18" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K18" s="10">
+        <v>9</v>
+      </c>
+      <c r="L18" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M18" s="10">
         <v>8.75</v>
       </c>
     </row>
@@ -10517,7 +10806,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10529,18 +10818,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10548,25 +10837,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -10574,19 +10863,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -10594,19 +10883,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -10614,13 +10903,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -10628,13 +10917,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F228B54-22D2-442D-966B-E03A22678980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6C40DD-A832-4495-B1FE-C2B2521AFAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -425,7 +425,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -482,6 +485,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -575,7 +581,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -632,6 +641,9 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -725,7 +737,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -782,6 +797,9 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -875,7 +893,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -932,6 +953,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1247,7 +1271,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1304,6 +1331,9 @@
                   <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1397,7 +1427,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1454,6 +1487,9 @@
                   <c:v>1.23</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1547,7 +1583,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1604,6 +1643,9 @@
                   <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1920,7 +1962,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2052,7 +2097,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2184,7 +2232,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2241,6 +2292,9 @@
                   <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
@@ -2558,7 +2612,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2615,6 +2672,9 @@
                   <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.78</c:v>
                 </c:pt>
               </c:numCache>
@@ -2708,7 +2768,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2765,6 +2828,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3080,7 +3146,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3137,6 +3206,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3230,7 +3302,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3287,6 +3362,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3380,7 +3458,10 @@
                   <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3437,6 +3518,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6890,7 +6974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
@@ -7762,10 +7846,10 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="C18" s="6">
         <v>0.75694444444444497</v>
@@ -7807,6 +7891,56 @@
         <v>13.1</v>
       </c>
       <c r="P18" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="12">
+        <v>39</v>
+      </c>
+      <c r="F19" s="12">
+        <v>35</v>
+      </c>
+      <c r="G19" s="12">
+        <v>37</v>
+      </c>
+      <c r="H19" s="12">
+        <v>37</v>
+      </c>
+      <c r="I19" s="12">
+        <v>33</v>
+      </c>
+      <c r="J19" s="12">
+        <v>35</v>
+      </c>
+      <c r="K19" s="12">
+        <v>36</v>
+      </c>
+      <c r="L19" s="12">
+        <v>32</v>
+      </c>
+      <c r="M19" s="12">
+        <v>34</v>
+      </c>
+      <c r="N19" s="12">
+        <v>22</v>
+      </c>
+      <c r="O19" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P19" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7825,7 +7959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
@@ -8554,10 +8688,10 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="C18" s="6">
         <v>0.75694444444444497</v>
@@ -8590,6 +8724,47 @@
         <v>1</v>
       </c>
       <c r="M18" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I19" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1</v>
+      </c>
+      <c r="M19" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -8607,7 +8782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
@@ -9336,10 +9511,10 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="C18" s="6">
         <v>0.75694444444444497</v>
@@ -9372,6 +9547,47 @@
         <v>0.33</v>
       </c>
       <c r="M18" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M19" s="8">
         <v>0.33</v>
       </c>
     </row>
@@ -9389,7 +9605,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
@@ -9977,10 +10193,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="C18" s="6">
         <v>0.75694444444444497</v>
@@ -10004,6 +10220,38 @@
         <v>0.75</v>
       </c>
       <c r="J18" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J19" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -10021,7 +10269,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
@@ -10752,10 +11000,10 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="13">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="C18" s="6">
         <v>0.75694444444444497</v>
@@ -10788,6 +11036,47 @@
         <v>8.5</v>
       </c>
       <c r="M18" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="10">
+        <v>11</v>
+      </c>
+      <c r="F19" s="10">
+        <v>10</v>
+      </c>
+      <c r="G19" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H19" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I19" s="10">
+        <v>17</v>
+      </c>
+      <c r="J19" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K19" s="10">
+        <v>9</v>
+      </c>
+      <c r="L19" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M19" s="10">
         <v>8.75</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6C40DD-A832-4495-B1FE-C2B2521AFAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E36647-2589-442F-A673-618C7C971470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -308,8 +308,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +327,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -430,6 +430,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -488,6 +491,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -586,6 +592,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -644,6 +653,9 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -742,6 +754,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -800,6 +815,9 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -898,6 +916,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -956,6 +977,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1173,7 +1197,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1276,6 +1300,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1335,6 +1362,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1432,6 +1462,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1491,6 +1524,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1588,6 +1624,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1647,6 +1686,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1864,7 +1906,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1967,6 +2009,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2102,6 +2147,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2237,6 +2285,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2295,6 +2346,9 @@
                   <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
@@ -2514,7 +2568,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2617,6 +2671,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2676,6 +2733,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2773,6 +2833,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2831,6 +2894,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3048,7 +3114,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3151,6 +3217,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3209,6 +3278,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3307,6 +3379,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3365,6 +3440,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3463,6 +3541,9 @@
                 <c:pt idx="16">
                   <c:v>46169</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46176</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3521,6 +3602,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6974,13 +7058,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
@@ -7941,6 +8025,56 @@
         <v>13.1</v>
       </c>
       <c r="P19" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="12">
+        <v>39</v>
+      </c>
+      <c r="F20" s="12">
+        <v>35</v>
+      </c>
+      <c r="G20" s="12">
+        <v>37</v>
+      </c>
+      <c r="H20" s="12">
+        <v>37</v>
+      </c>
+      <c r="I20" s="12">
+        <v>33</v>
+      </c>
+      <c r="J20" s="12">
+        <v>35</v>
+      </c>
+      <c r="K20" s="12">
+        <v>36</v>
+      </c>
+      <c r="L20" s="12">
+        <v>32</v>
+      </c>
+      <c r="M20" s="12">
+        <v>34</v>
+      </c>
+      <c r="N20" s="12">
+        <v>22</v>
+      </c>
+      <c r="O20" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P20" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7959,13 +8093,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -8766,6 +8900,47 @@
       </c>
       <c r="M19" s="8">
         <v>1.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.88</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1.18</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.98</v>
+      </c>
+      <c r="M20" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8782,13 +8957,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -9588,6 +9763,47 @@
         <v>0.33</v>
       </c>
       <c r="M19" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M20" s="8">
         <v>0.33</v>
       </c>
     </row>
@@ -9605,13 +9821,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -10255,6 +10471,38 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -10269,13 +10517,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="10" customWidth="1"/>
     <col min="6" max="13" width="9" style="10"/>
     <col min="14" max="21" width="9" style="8"/>
@@ -11077,6 +11325,47 @@
         <v>8.5</v>
       </c>
       <c r="M19" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46176</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="10">
+        <v>11</v>
+      </c>
+      <c r="F20" s="10">
+        <v>10</v>
+      </c>
+      <c r="G20" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H20" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I20" s="10">
+        <v>17</v>
+      </c>
+      <c r="J20" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K20" s="10">
+        <v>9</v>
+      </c>
+      <c r="L20" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M20" s="10">
         <v>8.75</v>
       </c>
     </row>
@@ -11095,7 +11384,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11107,9 +11396,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E36647-2589-442F-A673-618C7C971470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1675EFCB-8535-408E-8AD5-9825D33227AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -308,8 +308,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +327,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -433,6 +433,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -495,6 +498,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -595,6 +601,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -657,6 +666,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -757,6 +769,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -819,6 +834,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -919,6 +937,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -980,6 +1001,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1197,7 +1221,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1303,6 +1327,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1365,6 +1392,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1465,6 +1495,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1527,6 +1560,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1627,6 +1663,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1689,6 +1728,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1906,7 +1948,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2012,6 +2054,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2150,6 +2195,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2288,6 +2336,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2350,6 +2401,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2568,7 +2622,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2674,6 +2728,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2736,6 +2793,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2836,6 +2896,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2897,6 +2960,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3114,7 +3180,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3220,6 +3286,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3282,6 +3351,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3382,6 +3454,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3444,6 +3519,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3544,6 +3622,9 @@
                 <c:pt idx="17">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3606,6 +3687,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7058,13 +7142,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
@@ -8075,6 +8159,56 @@
         <v>13.1</v>
       </c>
       <c r="P20" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="12">
+        <v>37</v>
+      </c>
+      <c r="F21" s="12">
+        <v>35</v>
+      </c>
+      <c r="G21" s="12">
+        <v>36</v>
+      </c>
+      <c r="H21" s="12">
+        <v>35</v>
+      </c>
+      <c r="I21" s="12">
+        <v>33</v>
+      </c>
+      <c r="J21" s="12">
+        <v>34</v>
+      </c>
+      <c r="K21" s="12">
+        <v>33</v>
+      </c>
+      <c r="L21" s="12">
+        <v>31</v>
+      </c>
+      <c r="M21" s="12">
+        <v>32</v>
+      </c>
+      <c r="N21" s="12">
+        <v>22</v>
+      </c>
+      <c r="O21" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P21" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -8093,13 +8227,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -8941,6 +9075,47 @@
       </c>
       <c r="M20" s="8">
         <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.88</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.88</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1.17</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1.18</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.98</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -8957,13 +9132,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -9805,6 +9980,47 @@
       </c>
       <c r="M20" s="8">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.31</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0.315</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.31</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0.315</v>
       </c>
     </row>
   </sheetData>
@@ -9821,13 +10037,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -10500,6 +10716,38 @@
         <v>0.75</v>
       </c>
       <c r="J20" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.74</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J21" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -10517,13 +10765,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="10" customWidth="1"/>
     <col min="6" max="13" width="9" style="10"/>
     <col min="14" max="21" width="9" style="8"/>
@@ -11367,6 +11615,47 @@
       </c>
       <c r="M20" s="10">
         <v>8.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46183</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="F21" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>10</v>
+      </c>
+      <c r="H21" s="10">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10">
+        <v>16</v>
+      </c>
+      <c r="J21" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="K21" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="L21" s="10">
+        <v>8</v>
+      </c>
+      <c r="M21" s="10">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11384,7 +11673,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11396,9 +11685,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
